--- a/artfynd/A 11355-2026 artfynd.xlsx
+++ b/artfynd/A 11355-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131914344</v>
+        <v>131914412</v>
       </c>
       <c r="B2" t="n">
-        <v>101323</v>
+        <v>96410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2812</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469686</v>
+        <v>469661</v>
       </c>
       <c r="R2" t="n">
-        <v>7013104</v>
+        <v>7013115</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Mycket rikligt i markskiktet i området</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131914469</v>
+        <v>131947477</v>
       </c>
       <c r="B3" t="n">
-        <v>92868</v>
+        <v>96410</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rödön, Rödön, Jmt</t>
+          <t>Rödögården, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469643</v>
+        <v>469614</v>
       </c>
       <c r="R3" t="n">
-        <v>7013046</v>
+        <v>7013029</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,31 +855,16 @@
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Fjolårsfruktkroppar. Mest sannolikt.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -882,69 +872,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131914272</v>
+        <v>131914469</v>
       </c>
       <c r="B4" t="n">
-        <v>58114</v>
+        <v>92943</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rödön, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469739</v>
+        <v>469643</v>
       </c>
       <c r="R4" t="n">
-        <v>7013135</v>
+        <v>7013046</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,19 +964,19 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spelande.</t>
+          <t>Fjolårsfruktkroppar. Mest sannolikt.</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -1015,48 +996,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131947473</v>
+        <v>131914272</v>
       </c>
       <c r="B5" t="n">
-        <v>101325</v>
+        <v>58136</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rödögården, Jmt</t>
+          <t>Rödön, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469614</v>
+        <v>469739</v>
       </c>
       <c r="R5" t="n">
-        <v>7013029</v>
+        <v>7013135</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,9 +1073,24 @@
           <t>2026-03-25</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spelande.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,15 +1105,442 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131914476</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rödön, Rödön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>469617</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7013081</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131914261</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rödön, Rödön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>469718</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7013185</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131914344</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rödön, Rödön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>469686</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7013104</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131947473</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rödögården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>469614</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7013029</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Maria Danvind</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Maria Danvind</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11355-2026 artfynd.xlsx
+++ b/artfynd/A 11355-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131914412</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131947477</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131914469</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,6 +1134,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131914272</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1230,6 +1255,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131914476</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1337,6 +1367,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131914261</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1444,6 +1479,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131914344</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1541,8 +1581,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131947473</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>